--- a/public/tally_templates/YKTD.xlsx
+++ b/public/tally_templates/YKTD.xlsx
@@ -1387,7 +1387,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
@@ -3354,7 +3354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="699">
+  <cellXfs count="727">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5414,6 +5414,90 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5421,11 +5505,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5815,7 +5899,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y106"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -6624,7 +6708,7 @@
       <c r="G8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="700" t="s">
         <v>139</v>
       </c>
       <c r="I8" s="12"/>
@@ -7982,7 +8066,7 @@
       <c r="G56" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="H56" s="700" t="s">
         <v>139</v>
       </c>
       <c r="I56" s="12"/>
@@ -8107,27 +8191,17 @@
       <c r="Y59" s="1"/>
     </row>
     <row r="60" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A60" s="458" t="s">
-        <v>149</v>
-      </c>
+      <c r="A60" s="458"/>
       <c r="B60" s="459"/>
-      <c r="C60" s="410" t="s">
-        <v>150</v>
-      </c>
+      <c r="C60" s="410"/>
       <c r="D60" s="53"/>
       <c r="E60" s="53"/>
-      <c r="F60" s="460">
-        <v>-18</v>
-      </c>
-      <c r="G60" s="460">
-        <v>-15.3</v>
-      </c>
+      <c r="F60" s="460"/>
+      <c r="G60" s="460"/>
       <c r="H60" s="412" t="s">
         <v>151</v>
       </c>
-      <c r="I60" s="461" t="s">
-        <v>152</v>
-      </c>
+      <c r="I60" s="461"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -8146,27 +8220,15 @@
       <c r="Y60" s="1"/>
     </row>
     <row r="61" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A61" s="462" t="s">
-        <v>153</v>
-      </c>
+      <c r="A61" s="462"/>
       <c r="B61" s="463"/>
-      <c r="C61" s="413" t="s">
-        <v>150</v>
-      </c>
+      <c r="C61" s="413"/>
       <c r="D61" s="292"/>
       <c r="E61" s="292"/>
-      <c r="F61" s="424">
-        <v>-18</v>
-      </c>
-      <c r="G61" s="424">
-        <v>-15.5</v>
-      </c>
-      <c r="H61" s="415" t="s">
-        <v>154</v>
-      </c>
-      <c r="I61" s="464" t="s">
-        <v>152</v>
-      </c>
+      <c r="F61" s="424"/>
+      <c r="G61" s="424"/>
+      <c r="H61" s="415"/>
+      <c r="I61" s="464"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -8185,27 +8247,15 @@
       <c r="Y61" s="1"/>
     </row>
     <row r="62" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A62" s="465" t="s">
-        <v>155</v>
-      </c>
+      <c r="A62" s="465"/>
       <c r="B62" s="463"/>
-      <c r="C62" s="413" t="s">
-        <v>150</v>
-      </c>
+      <c r="C62" s="413"/>
       <c r="D62" s="292"/>
       <c r="E62" s="292"/>
-      <c r="F62" s="424">
-        <v>-18</v>
-      </c>
-      <c r="G62" s="424">
-        <v>-15.4</v>
-      </c>
-      <c r="H62" s="415" t="s">
-        <v>154</v>
-      </c>
-      <c r="I62" s="464" t="s">
-        <v>156</v>
-      </c>
+      <c r="F62" s="424"/>
+      <c r="G62" s="424"/>
+      <c r="H62" s="415"/>
+      <c r="I62" s="464"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -8224,27 +8274,15 @@
       <c r="Y62" s="1"/>
     </row>
     <row r="63" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A63" s="465" t="s">
-        <v>157</v>
-      </c>
+      <c r="A63" s="465"/>
       <c r="B63" s="463"/>
-      <c r="C63" s="413" t="s">
-        <v>150</v>
-      </c>
+      <c r="C63" s="413"/>
       <c r="D63" s="292"/>
       <c r="E63" s="292"/>
-      <c r="F63" s="424">
-        <v>-18</v>
-      </c>
-      <c r="G63" s="424">
-        <v>-16.3</v>
-      </c>
-      <c r="H63" s="415" t="s">
-        <v>154</v>
-      </c>
-      <c r="I63" s="464" t="s">
-        <v>156</v>
-      </c>
+      <c r="F63" s="424"/>
+      <c r="G63" s="424"/>
+      <c r="H63" s="415"/>
+      <c r="I63" s="464"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -8263,27 +8301,15 @@
       <c r="Y63" s="1"/>
     </row>
     <row r="64" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A64" s="466" t="s">
-        <v>158</v>
-      </c>
+      <c r="A64" s="466"/>
       <c r="B64" s="467"/>
-      <c r="C64" s="467" t="s">
-        <v>150</v>
-      </c>
+      <c r="C64" s="467"/>
       <c r="D64" s="416"/>
       <c r="E64" s="416"/>
-      <c r="F64" s="426">
-        <v>-18</v>
-      </c>
-      <c r="G64" s="426">
-        <v>-18</v>
-      </c>
-      <c r="H64" s="420" t="s">
-        <v>154</v>
-      </c>
-      <c r="I64" s="468" t="s">
-        <v>156</v>
-      </c>
+      <c r="F64" s="426"/>
+      <c r="G64" s="426"/>
+      <c r="H64" s="420"/>
+      <c r="I64" s="468"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -8302,27 +8328,15 @@
       <c r="Y64" s="1"/>
     </row>
     <row r="65" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A65" s="469" t="s">
-        <v>159</v>
-      </c>
+      <c r="A65" s="469"/>
       <c r="B65" s="459"/>
-      <c r="C65" s="459" t="s">
-        <v>150</v>
-      </c>
+      <c r="C65" s="459"/>
       <c r="D65" s="53"/>
       <c r="E65" s="53"/>
-      <c r="F65" s="470">
-        <v>-18</v>
-      </c>
-      <c r="G65" s="471">
-        <v>-17.8</v>
-      </c>
-      <c r="H65" s="412" t="s">
-        <v>154</v>
-      </c>
-      <c r="I65" s="461" t="s">
-        <v>156</v>
-      </c>
+      <c r="F65" s="470"/>
+      <c r="G65" s="471"/>
+      <c r="H65" s="412"/>
+      <c r="I65" s="461"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -8341,27 +8355,15 @@
       <c r="Y65" s="1"/>
     </row>
     <row r="66" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A66" s="465" t="s">
-        <v>160</v>
-      </c>
+      <c r="A66" s="465"/>
       <c r="B66" s="422"/>
-      <c r="C66" s="413" t="s">
-        <v>150</v>
-      </c>
+      <c r="C66" s="413"/>
       <c r="D66" s="292"/>
       <c r="E66" s="292"/>
-      <c r="F66" s="424">
-        <v>-18</v>
-      </c>
-      <c r="G66" s="423">
-        <v>-18.6</v>
-      </c>
-      <c r="H66" s="415" t="s">
-        <v>154</v>
-      </c>
-      <c r="I66" s="464" t="s">
-        <v>156</v>
-      </c>
+      <c r="F66" s="424"/>
+      <c r="G66" s="423"/>
+      <c r="H66" s="415"/>
+      <c r="I66" s="464"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -8380,27 +8382,15 @@
       <c r="Y66" s="1"/>
     </row>
     <row r="67" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A67" s="465" t="s">
-        <v>161</v>
-      </c>
+      <c r="A67" s="465"/>
       <c r="B67" s="422"/>
-      <c r="C67" s="413" t="s">
-        <v>150</v>
-      </c>
+      <c r="C67" s="413"/>
       <c r="D67" s="292"/>
       <c r="E67" s="292"/>
-      <c r="F67" s="424">
-        <v>-18</v>
-      </c>
-      <c r="G67" s="424">
-        <v>-19</v>
-      </c>
-      <c r="H67" s="415" t="s">
-        <v>154</v>
-      </c>
-      <c r="I67" s="464" t="s">
-        <v>156</v>
-      </c>
+      <c r="F67" s="424"/>
+      <c r="G67" s="424"/>
+      <c r="H67" s="415"/>
+      <c r="I67" s="464"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -8419,27 +8409,15 @@
       <c r="Y67" s="1"/>
     </row>
     <row r="68" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A68" s="465" t="s">
-        <v>162</v>
-      </c>
+      <c r="A68" s="465"/>
       <c r="B68" s="422"/>
-      <c r="C68" s="413" t="s">
-        <v>150</v>
-      </c>
+      <c r="C68" s="413"/>
       <c r="D68" s="292"/>
       <c r="E68" s="292"/>
-      <c r="F68" s="424">
-        <v>-18</v>
-      </c>
-      <c r="G68" s="424">
-        <v>-17.4</v>
-      </c>
-      <c r="H68" s="415" t="s">
-        <v>154</v>
-      </c>
-      <c r="I68" s="464" t="s">
-        <v>156</v>
-      </c>
+      <c r="F68" s="424"/>
+      <c r="G68" s="424"/>
+      <c r="H68" s="415"/>
+      <c r="I68" s="464"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -8458,27 +8436,15 @@
       <c r="Y68" s="1"/>
     </row>
     <row r="69" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A69" s="466" t="s">
-        <v>163</v>
-      </c>
+      <c r="A69" s="466"/>
       <c r="B69" s="425"/>
-      <c r="C69" s="417" t="s">
-        <v>150</v>
-      </c>
+      <c r="C69" s="417"/>
       <c r="D69" s="416"/>
       <c r="E69" s="416"/>
-      <c r="F69" s="426">
-        <v>-18</v>
-      </c>
-      <c r="G69" s="426">
-        <v>-18.6</v>
-      </c>
-      <c r="H69" s="420" t="s">
-        <v>154</v>
-      </c>
-      <c r="I69" s="468" t="s">
-        <v>156</v>
-      </c>
+      <c r="F69" s="426"/>
+      <c r="G69" s="426"/>
+      <c r="H69" s="420"/>
+      <c r="I69" s="468"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -8497,27 +8463,15 @@
       <c r="Y69" s="1"/>
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A70" s="469" t="s">
-        <v>164</v>
-      </c>
+      <c r="A70" s="469"/>
       <c r="B70" s="472"/>
-      <c r="C70" s="459" t="s">
-        <v>150</v>
-      </c>
+      <c r="C70" s="459"/>
       <c r="D70" s="53"/>
       <c r="E70" s="53"/>
-      <c r="F70" s="470">
-        <v>-18</v>
-      </c>
-      <c r="G70" s="471">
-        <v>-17.7</v>
-      </c>
-      <c r="H70" s="412" t="s">
-        <v>154</v>
-      </c>
-      <c r="I70" s="461" t="s">
-        <v>156</v>
-      </c>
+      <c r="F70" s="470"/>
+      <c r="G70" s="471"/>
+      <c r="H70" s="412"/>
+      <c r="I70" s="461"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -8536,27 +8490,15 @@
       <c r="Y70" s="1"/>
     </row>
     <row r="71" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A71" s="465" t="s">
-        <v>165</v>
-      </c>
+      <c r="A71" s="465"/>
       <c r="B71" s="422"/>
-      <c r="C71" s="413" t="s">
-        <v>150</v>
-      </c>
+      <c r="C71" s="413"/>
       <c r="D71" s="292"/>
       <c r="E71" s="292"/>
-      <c r="F71" s="424">
-        <v>-18</v>
-      </c>
-      <c r="G71" s="423">
-        <v>-15</v>
-      </c>
-      <c r="H71" s="415" t="s">
-        <v>154</v>
-      </c>
-      <c r="I71" s="464" t="s">
-        <v>156</v>
-      </c>
+      <c r="F71" s="424"/>
+      <c r="G71" s="423"/>
+      <c r="H71" s="415"/>
+      <c r="I71" s="464"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -8575,27 +8517,15 @@
       <c r="Y71" s="1"/>
     </row>
     <row r="72" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A72" s="465" t="s">
-        <v>166</v>
-      </c>
+      <c r="A72" s="465"/>
       <c r="B72" s="422"/>
-      <c r="C72" s="413" t="s">
-        <v>150</v>
-      </c>
+      <c r="C72" s="413"/>
       <c r="D72" s="292"/>
       <c r="E72" s="292"/>
-      <c r="F72" s="424">
-        <v>-18</v>
-      </c>
-      <c r="G72" s="424">
-        <v>-18.6</v>
-      </c>
-      <c r="H72" s="415" t="s">
-        <v>154</v>
-      </c>
-      <c r="I72" s="464" t="s">
-        <v>156</v>
-      </c>
+      <c r="F72" s="424"/>
+      <c r="G72" s="424"/>
+      <c r="H72" s="415"/>
+      <c r="I72" s="464"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -8614,27 +8544,15 @@
       <c r="Y72" s="1"/>
     </row>
     <row r="73" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A73" s="465" t="s">
-        <v>167</v>
-      </c>
+      <c r="A73" s="465"/>
       <c r="B73" s="422"/>
-      <c r="C73" s="413" t="s">
-        <v>150</v>
-      </c>
+      <c r="C73" s="413"/>
       <c r="D73" s="292"/>
       <c r="E73" s="292"/>
-      <c r="F73" s="424">
-        <v>-18</v>
-      </c>
-      <c r="G73" s="424">
-        <v>-17.7</v>
-      </c>
-      <c r="H73" s="415" t="s">
-        <v>154</v>
-      </c>
-      <c r="I73" s="464" t="s">
-        <v>156</v>
-      </c>
+      <c r="F73" s="424"/>
+      <c r="G73" s="424"/>
+      <c r="H73" s="415"/>
+      <c r="I73" s="464"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -8653,27 +8571,15 @@
       <c r="Y73" s="1"/>
     </row>
     <row r="74" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A74" s="473" t="s">
-        <v>168</v>
-      </c>
+      <c r="A74" s="473"/>
       <c r="B74" s="425"/>
-      <c r="C74" s="417" t="s">
-        <v>150</v>
-      </c>
+      <c r="C74" s="417"/>
       <c r="D74" s="416"/>
       <c r="E74" s="416"/>
-      <c r="F74" s="426">
-        <v>-18</v>
-      </c>
-      <c r="G74" s="426">
-        <v>-15.5</v>
-      </c>
-      <c r="H74" s="420" t="s">
-        <v>154</v>
-      </c>
-      <c r="I74" s="468" t="s">
-        <v>152</v>
-      </c>
+      <c r="F74" s="426"/>
+      <c r="G74" s="426"/>
+      <c r="H74" s="420"/>
+      <c r="I74" s="468"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -9649,7 +9555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -10448,7 +10354,7 @@
       <c r="A8" s="193" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="193" t="s">
+      <c r="B8" s="161" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="193"/>
@@ -10460,7 +10366,7 @@
         <v>62</v>
       </c>
       <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="161" t="s">
         <v>63</v>
       </c>
       <c r="K8" s="8"/>
@@ -10511,7 +10417,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="198" t="s">
         <v>11</v>
       </c>
@@ -10552,7 +10458,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="202"/>
       <c r="B11" s="202"/>
       <c r="C11" s="261"/>
@@ -11366,7 +11272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -11723,7 +11629,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="699" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -11732,14 +11638,14 @@
       <c r="F4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="700"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="1"/>
       <c r="K4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="701"/>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
@@ -11785,21 +11691,21 @@
       <c r="A6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="702"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="700"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="1"/>
       <c r="K6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="703" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="18"/>
@@ -14511,7 +14417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
@@ -15190,7 +15096,7 @@
       <c r="O6" s="253" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="40"/>
+      <c r="P6" s="725"/>
       <c r="Q6" s="40"/>
       <c r="R6" s="120" t="str">
         <f>'Final Work'!G4</f>
@@ -15264,7 +15170,7 @@
       </c>
       <c r="B8" s="489"/>
       <c r="C8" s="489"/>
-      <c r="D8" s="489" t="s">
+      <c r="D8" s="726" t="s">
         <v>63</v>
       </c>
       <c r="E8" s="489"/>
@@ -15280,7 +15186,7 @@
       <c r="O8" s="489" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="490"/>
+      <c r="P8" s="726"/>
       <c r="Q8" s="490"/>
       <c r="R8" s="488">
         <f>'Final Work'!G6</f>
@@ -15297,7 +15203,7 @@
       </c>
       <c r="Z8" s="488"/>
       <c r="AA8" s="488"/>
-      <c r="AB8" s="488" t="s">
+      <c r="AB8" s="726" t="s">
         <v>25</v>
       </c>
       <c r="AC8" s="488"/>
@@ -20052,7 +19958,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -20851,7 +20757,7 @@
       <c r="A8" s="193" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="193" t="s">
+      <c r="B8" s="161" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="193"/>
@@ -20863,7 +20769,7 @@
         <v>62</v>
       </c>
       <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="161" t="s">
         <v>63</v>
       </c>
       <c r="K8" s="8"/>
@@ -20914,7 +20820,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="195" t="s">
         <v>11</v>
       </c>
@@ -20955,7 +20861,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="199"/>
       <c r="B11" s="199"/>
       <c r="C11" s="261"/>
@@ -21769,7 +21675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y110"/>
   <sheetFormatPr defaultRowHeight="12" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -22627,20 +22533,20 @@
       <c r="A8" s="310" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="310"/>
+      <c r="B8" s="721"/>
       <c r="C8" s="313"/>
       <c r="D8" s="313"/>
       <c r="E8" s="313"/>
       <c r="F8" s="310" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="310"/>
+      <c r="G8" s="721"/>
       <c r="H8" s="310"/>
       <c r="I8" s="310"/>
       <c r="J8" s="310" t="s">
         <v>82</v>
       </c>
-      <c r="K8" s="311" t="s">
+      <c r="K8" s="313" t="s">
         <v>13</v>
       </c>
       <c r="L8" s="311" t="s">
@@ -23320,7 +23226,7 @@
       </c>
       <c r="B33" s="323"/>
       <c r="C33" s="323"/>
-      <c r="D33" s="324"/>
+      <c r="D33" s="722"/>
       <c r="E33" s="324"/>
       <c r="F33" s="324"/>
       <c r="G33" s="324"/>
@@ -23912,7 +23818,7 @@
       <c r="X52" s="329"/>
       <c r="Y52" s="329"/>
     </row>
-    <row r="53" ht="14.25" customHeight="1" spans="1:25" s="329" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="16.2" customHeight="1" spans="1:25" s="329" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="348" t="s">
         <v>22</v>
       </c>
@@ -24159,20 +24065,20 @@
       <c r="A61" s="310" t="s">
         <v>80</v>
       </c>
-      <c r="B61" s="310"/>
+      <c r="B61" s="721"/>
       <c r="C61" s="313"/>
       <c r="D61" s="313"/>
       <c r="E61" s="313"/>
       <c r="F61" s="310" t="s">
         <v>81</v>
       </c>
-      <c r="G61" s="310"/>
+      <c r="G61" s="721"/>
       <c r="H61" s="310"/>
       <c r="I61" s="310"/>
       <c r="J61" s="310" t="s">
         <v>82</v>
       </c>
-      <c r="K61" s="311" t="s">
+      <c r="K61" s="313" t="s">
         <v>13</v>
       </c>
       <c r="L61" s="311" t="s">
@@ -24852,7 +24758,7 @@
       </c>
       <c r="B86" s="323"/>
       <c r="C86" s="323"/>
-      <c r="D86" s="324"/>
+      <c r="D86" s="722"/>
       <c r="E86" s="324"/>
       <c r="F86" s="324"/>
       <c r="G86" s="324"/>
@@ -25417,7 +25323,7 @@
       <c r="X104" s="305"/>
       <c r="Y104" s="305"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="105" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="348" t="s">
         <v>22</v>
       </c>
@@ -25657,7 +25563,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -26451,7 +26357,7 @@
       <c r="A6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="193" t="s">
+      <c r="B6" s="161" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -26461,13 +26367,13 @@
       <c r="G6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="8"/>
+      <c r="H6" s="161"/>
       <c r="I6" s="8"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="194"/>
+      <c r="L6" s="710"/>
       <c r="M6" s="8"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -26513,7 +26419,7 @@
       <c r="A8" s="193" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="711" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="3"/>
@@ -26523,13 +26429,13 @@
       <c r="G8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="8"/>
+      <c r="H8" s="161"/>
       <c r="I8" s="8"/>
       <c r="J8" s="3"/>
       <c r="K8" s="193" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="8"/>
+      <c r="L8" s="161"/>
       <c r="M8" s="8"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -26650,15 +26556,15 @@
       <c r="B12" s="204"/>
       <c r="C12" s="205"/>
       <c r="D12" s="206"/>
-      <c r="E12" s="207"/>
-      <c r="F12" s="208"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="214"/>
       <c r="G12" s="209"/>
       <c r="H12" s="210"/>
       <c r="I12" s="211"/>
       <c r="J12" s="210"/>
       <c r="K12" s="203"/>
       <c r="L12" s="203"/>
-      <c r="M12" s="212"/>
+      <c r="M12" s="712"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -26677,15 +26583,15 @@
       <c r="B13" s="206"/>
       <c r="C13" s="214"/>
       <c r="D13" s="206"/>
-      <c r="E13" s="207"/>
-      <c r="F13" s="208"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="214"/>
       <c r="G13" s="209"/>
       <c r="H13" s="215"/>
       <c r="I13" s="216"/>
       <c r="J13" s="210"/>
       <c r="K13" s="213"/>
       <c r="L13" s="213"/>
-      <c r="M13" s="217"/>
+      <c r="M13" s="713"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -26704,15 +26610,15 @@
       <c r="B14" s="206"/>
       <c r="C14" s="214"/>
       <c r="D14" s="206"/>
-      <c r="E14" s="207"/>
-      <c r="F14" s="208"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="214"/>
       <c r="G14" s="209"/>
       <c r="H14" s="210"/>
       <c r="I14" s="211"/>
       <c r="J14" s="210"/>
       <c r="K14" s="209"/>
       <c r="L14" s="213"/>
-      <c r="M14" s="218"/>
+      <c r="M14" s="714"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -26731,15 +26637,15 @@
       <c r="B15" s="206"/>
       <c r="C15" s="214"/>
       <c r="D15" s="206"/>
-      <c r="E15" s="207"/>
-      <c r="F15" s="208"/>
+      <c r="E15" s="358"/>
+      <c r="F15" s="214"/>
       <c r="G15" s="209"/>
       <c r="H15" s="210"/>
       <c r="I15" s="211"/>
       <c r="J15" s="210"/>
       <c r="K15" s="209"/>
       <c r="L15" s="209"/>
-      <c r="M15" s="218"/>
+      <c r="M15" s="714"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -26758,15 +26664,15 @@
       <c r="B16" s="206"/>
       <c r="C16" s="214"/>
       <c r="D16" s="206"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="208"/>
+      <c r="E16" s="358"/>
+      <c r="F16" s="214"/>
       <c r="G16" s="209"/>
       <c r="H16" s="210"/>
       <c r="I16" s="211"/>
       <c r="J16" s="210"/>
       <c r="K16" s="209"/>
       <c r="L16" s="209"/>
-      <c r="M16" s="218"/>
+      <c r="M16" s="714"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -26785,15 +26691,15 @@
       <c r="B17" s="206"/>
       <c r="C17" s="214"/>
       <c r="D17" s="206"/>
-      <c r="E17" s="207"/>
-      <c r="F17" s="208"/>
+      <c r="E17" s="358"/>
+      <c r="F17" s="214"/>
       <c r="G17" s="209"/>
       <c r="H17" s="210"/>
       <c r="I17" s="211"/>
       <c r="J17" s="210"/>
       <c r="K17" s="209"/>
       <c r="L17" s="209"/>
-      <c r="M17" s="218"/>
+      <c r="M17" s="714"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -26812,15 +26718,15 @@
       <c r="B18" s="206"/>
       <c r="C18" s="214"/>
       <c r="D18" s="206"/>
-      <c r="E18" s="207"/>
-      <c r="F18" s="208"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="214"/>
       <c r="G18" s="209"/>
       <c r="H18" s="210"/>
       <c r="I18" s="211"/>
       <c r="J18" s="210"/>
       <c r="K18" s="209"/>
       <c r="L18" s="209"/>
-      <c r="M18" s="218"/>
+      <c r="M18" s="714"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -27614,7 +27520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -28408,7 +28314,7 @@
       <c r="A6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="193" t="s">
+      <c r="B6" s="161" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -28418,13 +28324,13 @@
       <c r="G6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="8"/>
+      <c r="H6" s="161"/>
       <c r="I6" s="8"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="194"/>
+      <c r="L6" s="710"/>
       <c r="M6" s="8"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -28470,7 +28376,7 @@
       <c r="A8" s="193" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="711" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="274"/>
@@ -28480,13 +28386,13 @@
       <c r="G8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="8"/>
+      <c r="H8" s="161"/>
       <c r="I8" s="8"/>
       <c r="J8" s="3"/>
       <c r="K8" s="193" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="8"/>
+      <c r="L8" s="161"/>
       <c r="M8" s="8"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -28607,8 +28513,8 @@
       <c r="B12" s="276"/>
       <c r="C12" s="277"/>
       <c r="D12" s="265"/>
-      <c r="E12" s="278"/>
-      <c r="F12" s="279"/>
+      <c r="E12" s="715"/>
+      <c r="F12" s="716"/>
       <c r="G12" s="264"/>
       <c r="H12" s="280"/>
       <c r="I12" s="281"/>
@@ -28634,15 +28540,15 @@
       <c r="B13" s="213"/>
       <c r="C13" s="213"/>
       <c r="D13" s="242"/>
-      <c r="E13" s="283"/>
-      <c r="F13" s="284"/>
+      <c r="E13" s="717"/>
+      <c r="F13" s="718"/>
       <c r="G13" s="213"/>
       <c r="H13" s="247"/>
       <c r="I13" s="285"/>
       <c r="J13" s="247"/>
       <c r="K13" s="213"/>
       <c r="L13" s="213"/>
-      <c r="M13" s="217"/>
+      <c r="M13" s="713"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -28661,15 +28567,15 @@
       <c r="B14" s="213"/>
       <c r="C14" s="213"/>
       <c r="D14" s="206"/>
-      <c r="E14" s="286"/>
-      <c r="F14" s="287"/>
+      <c r="E14" s="719"/>
+      <c r="F14" s="720"/>
       <c r="G14" s="209"/>
       <c r="H14" s="215"/>
       <c r="I14" s="216"/>
       <c r="J14" s="210"/>
       <c r="K14" s="209"/>
       <c r="L14" s="209"/>
-      <c r="M14" s="217"/>
+      <c r="M14" s="713"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -29523,7 +29429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y46"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -30187,11 +30093,11 @@
       <c r="A6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="149"/>
+      <c r="B6" s="703"/>
       <c r="C6" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="12"/>
+      <c r="D6" s="700"/>
       <c r="E6" s="12"/>
       <c r="F6" s="9"/>
       <c r="G6" s="151" t="s">
@@ -30250,17 +30156,17 @@
       <c r="A8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="153"/>
+      <c r="B8" s="700"/>
       <c r="C8" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="12"/>
+      <c r="D8" s="700"/>
       <c r="E8" s="12"/>
       <c r="F8" s="150"/>
       <c r="G8" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="18"/>
+      <c r="H8" s="703"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -30396,7 +30302,7 @@
     <row r="13" ht="18" customHeight="1" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="158"/>
       <c r="B13" s="159"/>
-      <c r="C13" s="160"/>
+      <c r="C13" s="704"/>
       <c r="D13" s="160"/>
       <c r="E13" s="160"/>
       <c r="F13" s="160"/>
@@ -30423,7 +30329,7 @@
     <row r="14" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="162"/>
       <c r="B14" s="163"/>
-      <c r="C14" s="164"/>
+      <c r="C14" s="705"/>
       <c r="D14" s="164"/>
       <c r="E14" s="164"/>
       <c r="F14" s="164"/>
@@ -30450,7 +30356,7 @@
     <row r="15" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="162"/>
       <c r="B15" s="56"/>
-      <c r="C15" s="165"/>
+      <c r="C15" s="706"/>
       <c r="D15" s="166"/>
       <c r="E15" s="166"/>
       <c r="F15" s="166"/>
@@ -30477,7 +30383,7 @@
     <row r="16" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="162"/>
       <c r="B16" s="56"/>
-      <c r="C16" s="165"/>
+      <c r="C16" s="706"/>
       <c r="D16" s="166"/>
       <c r="E16" s="166"/>
       <c r="F16" s="166"/>
@@ -30504,7 +30410,7 @@
     <row r="17" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="168"/>
       <c r="B17" s="169"/>
-      <c r="C17" s="170"/>
+      <c r="C17" s="707"/>
       <c r="D17" s="171"/>
       <c r="E17" s="171"/>
       <c r="F17" s="171"/>
@@ -30531,7 +30437,7 @@
     <row r="18" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="162"/>
       <c r="B18" s="56"/>
-      <c r="C18" s="165"/>
+      <c r="C18" s="706"/>
       <c r="D18" s="166"/>
       <c r="E18" s="166"/>
       <c r="F18" s="166"/>
@@ -30558,7 +30464,7 @@
     <row r="19" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="173"/>
       <c r="B19" s="56"/>
-      <c r="C19" s="165"/>
+      <c r="C19" s="706"/>
       <c r="D19" s="166"/>
       <c r="E19" s="166"/>
       <c r="F19" s="166"/>
@@ -30585,7 +30491,7 @@
     <row r="20" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="173"/>
       <c r="B20" s="174"/>
-      <c r="C20" s="175"/>
+      <c r="C20" s="708"/>
       <c r="D20" s="176"/>
       <c r="E20" s="176"/>
       <c r="F20" s="176"/>
@@ -30612,7 +30518,7 @@
     <row r="21" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="162"/>
       <c r="B21" s="174"/>
-      <c r="C21" s="175"/>
+      <c r="C21" s="708"/>
       <c r="D21" s="176"/>
       <c r="E21" s="176"/>
       <c r="F21" s="176"/>
@@ -30639,7 +30545,7 @@
     <row r="22" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="178"/>
       <c r="B22" s="169"/>
-      <c r="C22" s="170"/>
+      <c r="C22" s="707"/>
       <c r="D22" s="171"/>
       <c r="E22" s="171"/>
       <c r="F22" s="171"/>
@@ -30666,7 +30572,7 @@
     <row r="23" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="179"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="180"/>
+      <c r="C23" s="709"/>
       <c r="D23" s="181"/>
       <c r="E23" s="181"/>
       <c r="F23" s="181"/>
@@ -30693,7 +30599,7 @@
     <row r="24" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="183"/>
       <c r="B24" s="56"/>
-      <c r="C24" s="175"/>
+      <c r="C24" s="708"/>
       <c r="D24" s="176"/>
       <c r="E24" s="176"/>
       <c r="F24" s="176"/>
@@ -30720,7 +30626,7 @@
     <row r="25" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="183"/>
       <c r="B25" s="56"/>
-      <c r="C25" s="165"/>
+      <c r="C25" s="706"/>
       <c r="D25" s="166"/>
       <c r="E25" s="166"/>
       <c r="F25" s="166"/>
@@ -30747,7 +30653,7 @@
     <row r="26" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="162"/>
       <c r="B26" s="56"/>
-      <c r="C26" s="165"/>
+      <c r="C26" s="706"/>
       <c r="D26" s="166"/>
       <c r="E26" s="166"/>
       <c r="F26" s="166"/>
@@ -30774,7 +30680,7 @@
     <row r="27" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="168"/>
       <c r="B27" s="169"/>
-      <c r="C27" s="170"/>
+      <c r="C27" s="707"/>
       <c r="D27" s="171"/>
       <c r="E27" s="171"/>
       <c r="F27" s="171"/>
@@ -30801,7 +30707,7 @@
     <row r="28" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="29"/>
       <c r="B28" s="56"/>
-      <c r="C28" s="165"/>
+      <c r="C28" s="706"/>
       <c r="D28" s="166"/>
       <c r="E28" s="166"/>
       <c r="F28" s="166"/>
@@ -30828,7 +30734,7 @@
     <row r="29" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="162"/>
       <c r="B29" s="174"/>
-      <c r="C29" s="175"/>
+      <c r="C29" s="708"/>
       <c r="D29" s="176"/>
       <c r="E29" s="176"/>
       <c r="F29" s="176"/>
@@ -30857,7 +30763,7 @@
     <row r="30" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="162"/>
       <c r="B30" s="56"/>
-      <c r="C30" s="165"/>
+      <c r="C30" s="706"/>
       <c r="D30" s="166"/>
       <c r="E30" s="166"/>
       <c r="F30" s="166"/>
@@ -30884,7 +30790,7 @@
     <row r="31" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="162"/>
       <c r="B31" s="56"/>
-      <c r="C31" s="165"/>
+      <c r="C31" s="706"/>
       <c r="D31" s="166"/>
       <c r="E31" s="166"/>
       <c r="F31" s="166"/>
@@ -30911,7 +30817,7 @@
     <row r="32" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="184"/>
       <c r="B32" s="169"/>
-      <c r="C32" s="170"/>
+      <c r="C32" s="707"/>
       <c r="D32" s="171"/>
       <c r="E32" s="171"/>
       <c r="F32" s="171"/>
@@ -30938,7 +30844,7 @@
     <row r="33" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
       <c r="B33" s="56"/>
-      <c r="C33" s="165"/>
+      <c r="C33" s="706"/>
       <c r="D33" s="166"/>
       <c r="E33" s="166"/>
       <c r="F33" s="166"/>
@@ -30965,7 +30871,7 @@
     <row r="34" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="162"/>
       <c r="B34" s="56"/>
-      <c r="C34" s="165"/>
+      <c r="C34" s="706"/>
       <c r="D34" s="166"/>
       <c r="E34" s="166"/>
       <c r="F34" s="166"/>
@@ -30992,7 +30898,7 @@
     <row r="35" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="185"/>
       <c r="B35" s="56"/>
-      <c r="C35" s="165"/>
+      <c r="C35" s="706"/>
       <c r="D35" s="166"/>
       <c r="E35" s="166"/>
       <c r="F35" s="166"/>
@@ -31019,7 +30925,7 @@
     <row r="36" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="186"/>
       <c r="B36" s="56"/>
-      <c r="C36" s="165"/>
+      <c r="C36" s="706"/>
       <c r="D36" s="166"/>
       <c r="E36" s="166"/>
       <c r="F36" s="166"/>
@@ -31046,7 +30952,7 @@
     <row r="37" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="188"/>
       <c r="B37" s="169"/>
-      <c r="C37" s="170"/>
+      <c r="C37" s="707"/>
       <c r="D37" s="171"/>
       <c r="E37" s="171"/>
       <c r="F37" s="171"/>
@@ -31316,7 +31222,7 @@
       <c r="Y46" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="36">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -31351,6 +31257,8 @@
     <mergeCell ref="C37:H37"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="G41:H41"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.5118110236220472" footer="0.35433070866141736"/>
@@ -31359,7 +31267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -32039,7 +31947,7 @@
       <c r="F4" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="194"/>
+      <c r="G4" s="710"/>
       <c r="H4" s="8"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -32102,7 +32010,7 @@
       <c r="F6" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="353" t="s">
+      <c r="G6" s="723" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="3"/>
@@ -32745,12 +32653,12 @@
     <row r="29" ht="23.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="376"/>
       <c r="B29" s="377"/>
-      <c r="C29" s="378"/>
-      <c r="D29" s="378"/>
-      <c r="E29" s="378"/>
-      <c r="F29" s="378"/>
-      <c r="G29" s="378"/>
-      <c r="H29" s="378"/>
+      <c r="C29" s="724"/>
+      <c r="D29" s="724"/>
+      <c r="E29" s="724"/>
+      <c r="F29" s="724"/>
+      <c r="G29" s="724"/>
+      <c r="H29" s="724"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -32772,12 +32680,12 @@
     <row r="30" ht="23.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="376"/>
       <c r="B30" s="377"/>
-      <c r="C30" s="378"/>
-      <c r="D30" s="378"/>
-      <c r="E30" s="378"/>
-      <c r="F30" s="378"/>
-      <c r="G30" s="378"/>
-      <c r="H30" s="378"/>
+      <c r="C30" s="724"/>
+      <c r="D30" s="724"/>
+      <c r="E30" s="724"/>
+      <c r="F30" s="724"/>
+      <c r="G30" s="724"/>
+      <c r="H30" s="724"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -32799,12 +32707,12 @@
     <row r="31" ht="23.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="376"/>
       <c r="B31" s="377"/>
-      <c r="C31" s="378"/>
-      <c r="D31" s="378"/>
-      <c r="E31" s="378"/>
-      <c r="F31" s="378"/>
-      <c r="G31" s="378"/>
-      <c r="H31" s="378"/>
+      <c r="C31" s="724"/>
+      <c r="D31" s="724"/>
+      <c r="E31" s="724"/>
+      <c r="F31" s="724"/>
+      <c r="G31" s="724"/>
+      <c r="H31" s="724"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -33171,7 +33079,7 @@
       <c r="F43" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G43" s="353" t="s">
+      <c r="G43" s="723" t="s">
         <v>25</v>
       </c>
       <c r="H43" s="3"/>
